--- a/data/trans_dic/P1419-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1419-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,49</t>
+          <t>2,02; 6,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,82</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,06</t>
+          <t>0,3; 3,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,35</t>
+          <t>0,22; 2,2</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 15,52</t>
+          <t>7,32; 15,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 8,81</t>
+          <t>3,01; 9,57</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,15; 10,53</t>
+          <t>4,5; 10,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,17</t>
+          <t>0,94; 3,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,99; 9,73</t>
+          <t>5,16; 9,63</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,85</t>
+          <t>1,69; 4,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,54; 6,05</t>
+          <t>2,63; 6,28</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,21</t>
+          <t>0,76; 2,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,43</t>
+          <t>2,21; 6,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,23</t>
+          <t>0,59; 3,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,72; 4,68</t>
+          <t>1,6; 4,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,44</t>
+          <t>8,0; 13,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,83; 8,41</t>
+          <t>3,97; 8,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 4,4</t>
+          <t>1,07; 4,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,2; 12,73</t>
+          <t>8,17; 12,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 9,06</t>
+          <t>5,71; 9,14</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,05</t>
+          <t>2,59; 5,02</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,26</t>
+          <t>0,6; 2,2</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,09</t>
+          <t>5,37; 8,1</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,14</t>
+          <t>0,3; 2,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,95</t>
+          <t>0,32; 2,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 3,32</t>
+          <t>0,58; 3,46</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,34</t>
+          <t>2,39; 6,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 8,66</t>
+          <t>3,81; 9,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,74</t>
+          <t>2,4; 6,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 16,58</t>
+          <t>8,56; 16,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,29</t>
+          <t>6,27; 10,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,51</t>
+          <t>2,16; 5,05</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,36</t>
+          <t>1,75; 4,5</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,82; 9,0</t>
+          <t>5,04; 9,27</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,61; 7,77</t>
+          <t>4,91; 7,9</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>0,71; 4,12</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0,26; 3,31</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>0,7; 3,75</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>0,26; 3,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,75; 3,7</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,8; 4,57</t>
+          <t>0,99; 4,71</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,23; 15,7</t>
+          <t>9,29; 15,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 15,83</t>
+          <t>8,8; 16,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,11; 11,2</t>
+          <t>4,99; 11,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,15; 7,46</t>
+          <t>4,98; 8,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,43; 8,91</t>
+          <t>5,37; 9,01</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4,98; 8,81</t>
+          <t>4,9; 8,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,54</t>
+          <t>3,24; 6,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,43</t>
+          <t>3,4; 6,01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,43; 4,02</t>
+          <t>0,43; 4,32</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,55</t>
+          <t>0,85; 5,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,97; 9,72</t>
+          <t>3,95; 9,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,11; 11,74</t>
+          <t>4,26; 12,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,31; 22,13</t>
+          <t>12,45; 22,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 6,27</t>
+          <t>1,34; 5,99</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>17,44; 24,44</t>
+          <t>16,35; 23,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 7,28</t>
+          <t>2,66; 6,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,47; 13,14</t>
+          <t>7,14; 13,23</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,29</t>
+          <t>1,32; 4,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,69; 16,51</t>
+          <t>10,94; 15,48</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,81</t>
+          <t>0,63; 4,78</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,27</t>
+          <t>0,34; 2,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 3,35</t>
+          <t>0,3; 3,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2,46; 6,18</t>
+          <t>2,56; 6,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>8,18; 16,42</t>
+          <t>8,63; 16,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,15; 11,66</t>
+          <t>5,11; 11,63</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,83; 9,15</t>
+          <t>2,71; 8,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,8; 17,79</t>
+          <t>11,62; 17,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,32</t>
+          <t>4,92; 9,2</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,12; 6,51</t>
+          <t>3,06; 6,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,2</t>
+          <t>2,01; 5,33</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>7,61; 11,17</t>
+          <t>7,48; 10,99</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,7; 2,97</t>
+          <t>0,71; 2,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,22</t>
+          <t>0,31; 2,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 3,64</t>
+          <t>1,21; 3,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,79</t>
+          <t>6,36; 10,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,39</t>
+          <t>6,24; 10,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,72; 12,55</t>
+          <t>7,88; 12,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,67</t>
+          <t>3,96; 7,65</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>8,34; 23,02</t>
+          <t>19,56; 24,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,18</t>
+          <t>3,81; 6,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,1</t>
+          <t>4,5; 7,21</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,38</t>
+          <t>2,98; 5,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,23; 16,07</t>
+          <t>13,53; 17,0</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,63</t>
+          <t>4,24; 7,74</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,52; 2,01</t>
+          <t>0,52; 2,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,06</t>
+          <t>1,14; 3,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,45; 2,13</t>
+          <t>0,85; 2,51</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,57; 17,25</t>
+          <t>12,39; 17,72</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,86; 9,89</t>
+          <t>6,03; 9,71</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,21</t>
+          <t>5,25; 9,06</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,07</t>
+          <t>3,52; 6,01</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,04; 12,04</t>
+          <t>8,97; 12,03</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,6</t>
+          <t>3,42; 5,58</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,43; 5,57</t>
+          <t>3,51; 5,7</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,6</t>
+          <t>2,37; 3,85</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,64</t>
+          <t>2,44; 3,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,64</t>
+          <t>0,85; 1,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,97</t>
+          <t>1,15; 2,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2,71; 4,21</t>
+          <t>3,26; 4,45</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>9,8; 11,92</t>
+          <t>9,68; 11,85</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 9,48</t>
+          <t>7,55; 9,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,29; 7,08</t>
+          <t>5,34; 7,05</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,23; 11,15</t>
+          <t>10,17; 11,77</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,37; 7,6</t>
+          <t>6,3; 7,57</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4,32; 5,39</t>
+          <t>4,39; 5,43</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,43</t>
+          <t>3,4; 4,4</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6,03; 7,57</t>
+          <t>6,91; 7,97</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2597</t>
+          <t>2934</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7594</t>
+          <t>8596</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5435; 17728</t>
+          <t>5512; 17775</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 8316</t>
+          <t>0; 7714</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>880; 11941</t>
+          <t>877; 11098</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>749; 7309</t>
+          <t>704; 7000</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19634; 40474</t>
+          <t>19087; 40103</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8562; 25305</t>
+          <t>8633; 27496</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11972; 30398</t>
+          <t>12994; 31288</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2628; 9184</t>
+          <t>2959; 10410</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26623; 51968</t>
+          <t>27553; 51399</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9488; 28237</t>
+          <t>9844; 28805</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14789; 35265</t>
+          <t>15311; 36578</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4185; 13260</t>
+          <t>4839; 14207</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>15014</t>
+          <t>15453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>52623</t>
+          <t>55481</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>67637</t>
+          <t>70934</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11651; 31713</t>
+          <t>10881; 30805</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3025; 16338</t>
+          <t>2966; 15523</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5759</t>
+          <t>0; 6317</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8875; 24198</t>
+          <t>8458; 25521</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>40502; 67723</t>
+          <t>40294; 67899</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20064; 44059</t>
+          <t>20772; 43209</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5868; 23022</t>
+          <t>5582; 20912</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>42104; 65361</t>
+          <t>44546; 67916</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>57784; 90377</t>
+          <t>56948; 91168</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>26381; 51932</t>
+          <t>26625; 51641</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6401; 23218</t>
+          <t>6170; 22516</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>54479; 83369</t>
+          <t>57727; 87036</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12444</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27936</t>
+          <t>29579</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>40379</t>
+          <t>41923</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>947; 9998</t>
+          <t>946; 8064</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1037; 9551</t>
+          <t>1028; 9405</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1802; 10572</t>
+          <t>1856; 11013</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7528; 20022</t>
+          <t>7544; 19905</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12045; 29030</t>
+          <t>12788; 31079</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8572; 22977</t>
+          <t>8182; 23120</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29275; 55777</t>
+          <t>28803; 54089</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>20948; 35925</t>
+          <t>22348; 38355</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15129; 36043</t>
+          <t>14104; 33038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>11551; 28984</t>
+          <t>11626; 29935</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31552; 58915</t>
+          <t>33037; 60681</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>30655; 51714</t>
+          <t>33003; 53150</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25395</t>
+          <t>27801</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>31860</t>
+          <t>36286</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2519; 13463</t>
+          <t>2536; 14761</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>973; 13078</t>
+          <t>966; 12371</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2776; 13704</t>
+          <t>2581; 13892</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2506; 14291</t>
+          <t>3689; 17587</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>34279; 58301</t>
+          <t>34508; 58707</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34872; 61581</t>
+          <t>34214; 62477</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19785; 43376</t>
+          <t>19306; 43659</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>14990; 35480</t>
+          <t>21022; 36188</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39656; 65083</t>
+          <t>39235; 65790</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>37989; 67233</t>
+          <t>37385; 66932</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>24361; 49489</t>
+          <t>24552; 51048</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22213; 42798</t>
+          <t>27064; 47793</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11589</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>43056</t>
+          <t>44124</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>54646</t>
+          <t>57054</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>873; 8174</t>
+          <t>881; 8780</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2025; 11797</t>
+          <t>1817; 11027</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>997; 9016</t>
+          <t>993; 9027</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7105; 17368</t>
+          <t>8116; 19090</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>8543; 24387</t>
+          <t>8844; 24956</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>27034; 48599</t>
+          <t>27337; 48633</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>2982; 13714</t>
+          <t>2932; 13101</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>36325; 50904</t>
+          <t>37094; 52340</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10757; 29912</t>
+          <t>10929; 27922</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32288; 56784</t>
+          <t>30874; 57199</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5767; 18450</t>
+          <t>5666; 19068</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>45259; 63897</t>
+          <t>47312; 66960</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>10753</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>38213</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>47877</t>
+          <t>48966</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1065; 13038</t>
+          <t>1712; 12933</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>946; 8968</t>
+          <t>938; 8106</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>791; 8828</t>
+          <t>788; 8204</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6646; 16657</t>
+          <t>6921; 16486</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>22743; 45666</t>
+          <t>24016; 46031</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>14329; 32421</t>
+          <t>14206; 32339</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7716; 24983</t>
+          <t>7392; 23300</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>30250; 45619</t>
+          <t>30585; 46138</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>27286; 51172</t>
+          <t>26983; 50477</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17239; 35967</t>
+          <t>16903; 38185</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9325; 27862</t>
+          <t>10758; 28593</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>40028; 58746</t>
+          <t>39910; 58667</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>52513</t>
+          <t>60312</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>141848</t>
+          <t>167455</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>194361</t>
+          <t>227767</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4298; 18242</t>
+          <t>4389; 17161</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2022; 14722</t>
+          <t>2032; 15006</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>8216; 23884</t>
+          <t>7923; 23464</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40468; 67284</t>
+          <t>45718; 75557</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>39724; 66331</t>
+          <t>39828; 67261</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>53588; 87065</t>
+          <t>54684; 88512</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26698; 53033</t>
+          <t>27360; 52912</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>70852; 195460</t>
+          <t>150844; 189491</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>47790; 77499</t>
+          <t>47710; 78068</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>61132; 96315</t>
+          <t>60985; 97815</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40334; 72475</t>
+          <t>40141; 69017</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>121189; 236620</t>
+          <t>201638; 253259</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10751</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>38022</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>43896</t>
+          <t>50069</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>32220; 56717</t>
+          <t>31538; 57559</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4081; 15690</t>
+          <t>4072; 15782</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>8486; 23845</t>
+          <t>8910; 25053</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>4206; 19784</t>
+          <t>6766; 19998</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>98501; 135157</t>
+          <t>97042; 138802</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>48229; 81318</t>
+          <t>49595; 79850</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>43817; 76076</t>
+          <t>43371; 74853</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>25414; 43407</t>
+          <t>29239; 49914</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>138115; 183954</t>
+          <t>137013; 183806</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56403; 89724</t>
+          <t>54846; 89313</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>54983; 89377</t>
+          <t>56348; 91448</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>28227; 59167</t>
+          <t>38634; 62757</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>366375</t>
+          <t>406336</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>488249</t>
+          <t>541595</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>80228; 119234</t>
+          <t>79996; 120579</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28211; 56092</t>
+          <t>29023; 57158</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>39723; 66907</t>
+          <t>39141; 69582</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>93768; 145705</t>
+          <t>115239; 157044</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>331117; 402712</t>
+          <t>326983; 400540</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>268434; 337083</t>
+          <t>268396; 331839</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>187489; 251019</t>
+          <t>189281; 249845</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>301167; 407814</t>
+          <t>379438; 439184</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>424119; 505612</t>
+          <t>419464; 503578</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>301477; 376641</t>
+          <t>306249; 379222</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>238950; 307574</t>
+          <t>235967; 305143</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>428811; 538558</t>
+          <t>501568; 578599</t>
         </is>
       </c>
     </row>
